--- a/Config/Datas/Tables/d_地图_MapConfig.xlsx
+++ b/Config/Datas/Tables/d_地图_MapConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMap" sheetId="1" r:id="R60b924ae809645bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMap" sheetId="1" r:id="R05591db6bf594acc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1435,7 +1435,54 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="Q5" s="12">
-        <x:v>750</x:v>
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>劫雷试炼场</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="L6" t="n">
+        <x:v>3072</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>3072</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>20260906</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>420044;420045;420046;420047;420048;420049</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>40;20;10;10;10;10</x:v>
+      </x:c>
+      <x:c r="Q6">
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
